--- a/results/mummichog/BC_vs_PC/tables/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/mummichog/BC_vs_PC/tables/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>MODULE</t>
   </si>
@@ -37,61 +37,13 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>$Didemethylcitalopram$5-Hydroxyindoleacetaldehyde$$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Epinine; Deoxyepinephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$Dopamine$3-Methoxytyramine$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxykynurenamine$L-Normetanephrine$$Citalopram$Norepinephrine$Indole-3-acetaldehyde$Dopamine 3-O-sulfate$L-Metanephrine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$N-Methylphenylethanolamine$3,4-Dihydroxymandelaldehyde</t>
-  </si>
-  <si>
-    <t>CE2173,C16609,C05634,CE2172,C16608,C09642,C07453,C00788,C04043,C03758,C05587,C05583,C05638,C05589,CE2174,C07572,C00547,C00637,C13690,C05588,C05639,C03711,C05577</t>
-  </si>
-  <si>
-    <t>(15, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(3, 'Urea cycle/amino group metabolism')</t>
-  </si>
-  <si>
-    <t>module_2</t>
-  </si>
-  <si>
-    <t>O2'-4a-cyclic-tetrahydrobiopterin$$N-Methylserotonin$aminochrome o-semiquinone$L-Tyrosine$Dopamine$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$4-Hydroxy-2-quinolinecarboxylic acid$3,4-Dihydroxyphenylethyleneglycol$Formyl-5-hydroxykynurenamine$5-Hydroxyindoleacetate$5-Hydroxykynurenamine$3-Carbamoyl-2-phenylpropionaldehyde$5-S-glutathionyl-dopamine$L-Normetanephrine$3,4-Dihydroxymandelate$$Dopaquinone$L-Formylkynurenine$5-Hydroxy-L-tryptophan$adrenochrome o-semiquinone$L-Metanephrine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$N-Formylanthranilate$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$Indole-3-acetamide$Indole-3-acetate$Formyl-N-acetyl-5-methoxykynurenamine$Epinine; Deoxyepinephrine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate$3-Methoxytyramine$Melatonin; N-Acetyl-5-methoxytryptamine$3-O-methyldopa$beta-carboline$4-(2-Aminophenyl)-2,4-dioxobutanoate$5-Phenyl-1,3-oxazinane-2,4-dione$3-Methoxy-4-hydroxyphenylethyleneglycol$6,7-Dihydrobiopterin$noradrenochrome o-semiquinone$$noradrenochrome$L-Phenylalanine$dopaminochrome$Dopamine 3-O-sulfate$Indolepyruvate; Indolepyruvic acid; (Indol-3-yl)pyruvate; Indole-3-pyruvate; 3-(Indol-3-yl)pyruvate$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$$L-Kynurenine$5-Hydroxyindoleacetaldehyde$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$quinonoid dihydrobiopterin$2-Phenyl-1,3-propanediol monocarbamate$enol-Phenylpyruvate$$4-Hydroxyphenylacetate$5-methoxytryptophol$Norepinephrine$methyl indole-3-acetate$Phenylpyruvate$D-Tryptophan$N-Methylphenylethanolamine$Formylkynurenine$3,4-Dihydroxymandelaldehyde$5-Methoxyindoleacetate$Didemethylcitalopram$$adrenochrome$Homovanillate; Homovanillic acid$3-Methoxy-4-hydroxyphenylglycolaldehyde$3-(4-Hydroxyphenyl)pyruvate$Homogentisate$3-Carbamoyl-2-phenylpropionic acid$dopamine o-quinone$2-Hydroxyphenylacetate$5-hydroxytryptophol$Citalopram$$L-Tryptophan$6-Hydroxymelatonin$Indole-3-acetaldehyde$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$leukoaminochrome$Serotonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol</t>
-  </si>
-  <si>
-    <t>CE5236,CE2153,C06212,CE5277,C00082,C03758,C16595,C01717,C05576,C05647,C05635,C05638,C16587,CE5025,C05589,C05580,CE2174,C00822,C02700,C00643,CE5541,C05588,C00978,C05653,C05584,C02693,C00954,C05642,C07453,C00355,C04043,CE2119,C05350,C05587,C01598,CE2176,CE3087,C01252,C16596,C05594,C00268,CE5542,CE3140,CE5538,C00079,CE4888,C13690,C00331,C05604,CE2173,C00328,C05634,C16608,C09642,C00788,CE2705,C16586,C02763,CE5860,C00642,CE6205,C00547,CE2122,C00166,C00525,C03711,C02406,C05577,C05660,C16609,CE2172,CE5536,C05582,C05583,C01179,C00544,C16591,CE5276,C05852,CE1918,C07572,CE5982,C00078,C05643,C00637,C01161,CE5665,C00780,C05639</t>
-  </si>
-  <si>
-    <t>(43, 'Tyrosine metabolism');(35, 'Tryptophan metabolism');(8, 'Drug metabolism - cytochrome P450')</t>
-  </si>
-  <si>
-    <t>module_3</t>
-  </si>
-  <si>
-    <t>11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one$11beta,17alpha,21-Trihydroxypregnenolone$11beta-Hydroxyprogesterone$17alpha,21-Dihydroxypregnenolone$17alpha,20alpha-Dihydroxypregn-4-en-3-one$$3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA$16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$18-Hydroxycorticosterone$$11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione$Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M$17alpha-Hydroxypregnenolone$$Dehydroepiandrosterone$21-Hydroxypregnenolone$11-Deoxycortisol; Cortodoxone</t>
-  </si>
-  <si>
-    <t>C03205,C04295,C01953,C05489,C05498,C05487,C04518,C18075,C01227,C05140,C05497,C05139,C01176,C01124,C18038,C05284,C00735,C05138,C18045,dhea,C05485,C05488</t>
-  </si>
-  <si>
-    <t>(17, 'C21-steroid hormone biosynthesis and metabolism');(9, 'Androgen and estrogen biosynthesis and metabolism')</t>
-  </si>
-  <si>
-    <t>module_4</t>
-  </si>
-  <si>
-    <t>11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one$Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$11beta,17alpha,21-Trihydroxypregnenolone$Estradiol-17beta; beta-Estradiol; Estradiol$11beta-Hydroxyprogesterone$17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone$17alpha,21-Dihydroxypregnenolone$5beta-Dihydrotestosterone$11-Deoxycortisol; Cortodoxone$Testosterone glucuronide; Testosterone 17beta-(beta-D-glucuronide)$5alpha-Dihydrotestosterone$17alpha,20alpha-Dihydroxypregn-4-en-3-one$$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$androsterone glucuronide$3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one$2-hydroxy-3-methoxy-17beta-estradiol$5beta-Androstane-3,17-dione$Tetrahydrocorticosterone$Cortisone; 17alpha,21-Dihydroxy-4-pregnene-3,11,20-trione; Kendall's compound E; Reichstein's substance Fa$6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one$Testosterone$3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al$3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA$16-Glucuronide-estriol; 16alpha,17beta-Estriol 16-(beta-D-glucuronide)$19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one$5alpha-Androstane-3,17-dione; Androstanedione$16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$21-Hydroxypregnenolone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone$androsterone glucuronide$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Etiocholan-3alpha-ol-17-one 3-glucuronide$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$18-Hydroxycorticosterone$Androstenedione$Aldosterone; 11beta,21-Dihydroxy-3,20-dioxo-4-pregnen-18-al$$testosterone glucuronide$4,17 dihydroxy estradiol$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$17alpha-Hydroxyprogesterone$19-Hydroxyandrost-4-ene-3,17-dione; 19-Hydroxyandrostenedione$Etiocholan-3alpha-ol-17-one 3-glucuronide$11beta-Hydroxyandrost-4-ene-3,17-dione; Androst-4-ene-3,17-dione-11beta-ol; 4-Androsten-11beta-ol-3,17-dione$11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione$5alpha-androstane-3alpha,17beta-diol$5alpha-Dihydrotestosterone glucuronide$Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$17alpha-Hydroxypregnenolone$4-hydroxy-17beta-estradiol$4-methoxy-17beta-estradiol$11-Dehydrocorticosterone$$Dehydroepiandrosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$Progesterone; 4-Pregnene-3,20-dione$21-Hydroxy-5beta-pregnane-3,11,20-trione$Androsterone</t>
-  </si>
-  <si>
-    <t>C03205,C01953,C04295,C05489,C00951,C05498,C05469,C05487,C05293,C05488,C11134,C03917,C04518,C18075,C05301,andrstrnglc,C04373,CE2183,C03772,C05476,C00762,C14497,C00535,C05474,C01227,C05504,C05294,C00674,C05140,C05141,C05497,C05485,C02140,C04042,C11135,C00280,ahandrostanglc,C05139,C01176,C01124,andrstndn,C01780,C18038,tststeroneglc,hestratriol,C00468,17ahprgstrn,C05290,C11136,C05284,C05471,CE2209,5adtststeroneglc,C00735,C05475,C05478,C05473,C05138,CE2179,CE2186,C05490,C18045,dhea,C05472,C00410,C05477,C00523</t>
-  </si>
-  <si>
-    <t>(49, 'C21-steroid hormone biosynthesis and metabolism');(32, 'Androgen and estrogen biosynthesis and metabolism')</t>
-  </si>
-  <si>
-    <t>module_5</t>
-  </si>
-  <si>
-    <t>Aldosterone; 11beta,21-Dihydroxy-3,20-dioxo-4-pregnen-18-al$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone$5beta-Dihydrotestosterone$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$5beta-Androstane-3,17-dione$11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone$11-Dehydrocorticosterone$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$Progesterone; 4-Pregnene-3,20-dione$Tetrahydrocorticosterone$21-Hydroxy-5beta-pregnane-3,11,20-trione$Cortisone; 17alpha,21-Dihydroxy-4-pregnene-3,11,20-trione; Kendall's compound E; Reichstein's substance Fa$3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
-  </si>
-  <si>
-    <t>C01780,C05475,C05469,C05293,C05478,C03772,C05473,C05471,C02140,C04042,C05490,C05472,C00410,C05476,C05477,C00762,C05474</t>
-  </si>
-  <si>
-    <t>(16, 'C21-steroid hormone biosynthesis and metabolism');(2, 'Androgen and estrogen biosynthesis and metabolism')</t>
+    <t>11beta,17alpha,21-Trihydroxypregnenolone$21-Hydroxypregnenolone$Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one$11beta-Hydroxyprogesterone$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$17alpha-Hydroxypregnenolone$$11-Deoxycortisol; Cortodoxone$17alpha,20alpha-Dihydroxypregn-4-en-3-one$3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA$Dehydroepiandrosterone$16alpha-Hydroxyandrost-4-ene-3,17-dione; 4-Androsten-16alpha-ol-3,17-dione$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$17alpha,21-Dihydroxypregnenolone</t>
+  </si>
+  <si>
+    <t>C05489,C05485,C01953,C05498,C05497,C05138,C18038,C05488,C04518,C01227,dhea,C05140,C03205,C01176,C18045,C05139,C04295,C05487</t>
+  </si>
+  <si>
+    <t>(14, 'C21-steroid hormone biosynthesis and metabolism');(7, 'Androgen and estrogen biosynthesis and metabolism')</t>
   </si>
 </sst>
 </file>
@@ -423,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -451,10 +403,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.0005903187721369539</v>
+        <v>0.04209560697176638</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -464,86 +416,6 @@
       </c>
       <c r="F2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>0.001770956316410862</v>
-      </c>
-      <c r="C3">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>0.005903187721369539</v>
-      </c>
-      <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <v>0.01239669421487603</v>
-      </c>
-      <c r="C5">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>0.0436835891381346</v>
-      </c>
-      <c r="C6">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
